--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
@@ -151,7 +151,7 @@
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.chargeName}</t>
+    <t>{.shopChargeName}</t>
   </si>
   <si>
     <t>{.platformCode}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>订单类型</t>
   </si>
@@ -46,22 +46,10 @@
     <t>运输状态</t>
   </si>
   <si>
-    <t>实重</t>
-  </si>
-  <si>
-    <t>体积重</t>
-  </si>
-  <si>
-    <t>计费重</t>
-  </si>
-  <si>
-    <t>预估运费</t>
-  </si>
-  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
-    <t>实际运费[物流商]</t>
+    <t>实际运费</t>
   </si>
   <si>
     <t>实际报关费</t>
@@ -70,9 +58,6 @@
     <t>实际其他费用</t>
   </si>
   <si>
-    <t>运费差异</t>
-  </si>
-  <si>
     <t>平台</t>
   </si>
   <si>
@@ -118,18 +103,6 @@
     <t>{.transportStatusName}</t>
   </si>
   <si>
-    <t>{.actualWeight}</t>
-  </si>
-  <si>
-    <t>{.volumeWeight}</t>
-  </si>
-  <si>
-    <t>{.billingWeight}</t>
-  </si>
-  <si>
-    <t>{.estimatedShippingCost}</t>
-  </si>
-  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
@@ -140,9 +113,6 @@
   </si>
   <si>
     <t>{.actualOtherCost}</t>
-  </si>
-  <si>
-    <t>{.diffShippingCost}</t>
   </si>
   <si>
     <t>{.salesPlatform}</t>
@@ -1103,7 +1073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1111,23 +1081,18 @@
     <col min="3" max="3" width="14.875" customWidth="1"/>
     <col min="4" max="4" width="13.625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="13" width="20.75" customWidth="1"/>
-    <col min="14" max="14" width="16.75" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
-    <col min="16" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="15.75" customWidth="1"/>
-    <col min="20" max="20" width="13.875" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="23" width="13.125" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="9" width="20.75" customWidth="1"/>
+    <col min="10" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="14" max="14" width="15.75" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="13.75" customWidth="1"/>
+    <col min="17" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1185,94 +1150,64 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="L2" t="s">
+      <c r="Q2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" t="s">
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsLastMileCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>订单类型</t>
   </si>
@@ -85,6 +85,12 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>计费规则</t>
+  </si>
+  <si>
+    <t>账单确认日期</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -140,6 +146,12 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.feeRuleName}</t>
+  </si>
+  <si>
+    <t>{.confirmTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1073,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1092,7 +1104,7 @@
     <col min="17" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1150,64 +1162,76 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
